--- a/input/mapping/040. OCB_GOLD_TCKH_CST_LCS_KT_30D_FINAL_CASE5_MAPPING_MAIPT_BAOANH.xlsx
+++ b/input/mapping/040. OCB_GOLD_TCKH_CST_LCS_KT_30D_FINAL_CASE5_MAPPING_MAIPT_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAIPT\Downloads\MSSQL_TABLEAU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{922E743E-E59E-43DC-8D59-31E21285B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A282580D-41BB-4C6B-8A45-4A65843ECF48}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{922E743E-E59E-43DC-8D59-31E21285B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F834BDFE-2FBB-4BCC-BD00-A6233F8D929B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{057883CD-0FCA-40FE-915F-9A32094538F7}"/>
   </bookViews>
@@ -165,42 +165,8 @@
     <t>Code mới</t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CST_LCS_KT_30D_FINAL_CASE5 (
-    DATA_DT                 DATE,
-    CIF                     DECIMAL(10,0),
-    T_COMPANY_BOOK          STRING,
-    T_CREATE_DATE           DATE NOT NULL,
-    FINAL_STATUS            STRING,
-    SCTR                    DECIMAL(10,0),
-    T_DESCRIPTION           STRING,
-    CST_GRP                 STRING,
-    CUST_GROUP_NAME         STRING,
-    CUST_GROUP_LINE         STRING,
-    CUST_GROUP_LINE_SHORT   STRING,
-    TIENGUI                 DECIMAL(20,4),
-    TIENVAY                 DECIMAL(20,4),
-    CUST_CURRENT_ACCT_A1    DECIMAL(20,4),
-    CIF_LOANCLASS            DECIMAL(3,0),
-    DOANHSO_BAOLANH_30D     DECIMAL(31,4),
-    DOANHSO_LC_30D          DECIMAL(31,4),
-    NUM_TRANS               INT,
-    ACTIVE_INDEX            INT,
-    T24_STATUS              STRING,
-    T24_ACTIVE_RB           INT,
-    T24_ACTIVE_COMB         INT,
-    T24_ACTIVE_TRE          INT,
-    T24_ACTIVE_CIB          INT,
-    T24_ACTIVE_CMB          INT,
-    T24_ACTIVE_DCTC         INT,
-    T24_ACTIVE_LIO          INT,
-    W4_STATUS               STRING,
-    W4_ACTIVE_RB            INT,
-    W4_ACTIVE_LIO           INT,
-    DATE_SYS                TIMESTAMP
-)
-USING DELTA;
 INSERT INTO CST_LCS_KT_30D_FINAL_CASE5
 REPLACE WHERE DATA_DT = to_date(:DATADT, 'yyyyMMdd')
 WITH
@@ -341,7 +307,7 @@
 cte_cust_group AS (
     SELECT
         ocg.ref_code,
-        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name   -- cột 9
+        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name  
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ocbh_cus_group') ocg
     WHERE ocg.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ocg.ref_code
@@ -362,7 +328,7 @@
         max_by(ccb.so_du_bao_lanh, ccb.source_event_date) AS so_du_bao_lanh,
         max_by(ccb.so_du_lc,       ccb.source_event_date) AS so_du_lc
     FROM IDENTIFIER(:cleaned || '.business_vault.csat_customer_sum_balance') ccb
-    WHERE ccb.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    WHERE ccb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ccb.customer_hashkey
 ),
 cte_acct_base AS (   -- Bước 1
@@ -484,7 +450,7 @@
     LEFT JOIN cte_md_deal_sts_del d_md
       ON d_md.md_deal_hashkey = smdi.md_deal_hashkey
     WHERE smdi.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND smdi.t_value_date BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+      AND to_date(smdi.t_value_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
       AND d_md.md_deal_hashkey IS NULL
     GROUP BY smdi.md_deal_hashkey
 ),
@@ -499,10 +465,13 @@
       ON hmd.md_deal_hashkey = md1.md_deal_hashkey
     JOIN cte_snap_hub_crb hcb
       ON hcb.tieukhoan = hmd.business_key AND hcb.gl &lt;&gt; '9995'
+    LEFT JOIN cte_crb_sts_del d_crb                                   
+      ON d_crb.crb_hashkey = hcb.crb_hashkey                         
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance') scb
-      ON scb.crb_hashkey = hcb.crb_hashkey
-     AND scb.ma_key BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
-     AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    ON scb.crb_hashkey = hcb.crb_hashkey
+    AND to_date(scb.ma_key, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+    AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    WHERE d_crb.crb_hashkey IS NULL                                 
 ),
 cte_doanhso_baolanh_30d AS (  
     SELECT
@@ -519,7 +488,7 @@
         max_by(slct.t_issue_date, slct.source_event_date) AS t_issue_date
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_terms') slct
     WHERE slct.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND slct.t_issue_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
+    AND to_date(slct.t_issue_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
     GROUP BY slct.letter_of_credit_hashkey
 ),
 cte_lc_value AS (  
@@ -570,7 +539,7 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_currency') rc
       ON rc.id = v.t_lc_currency
      AND v.issue_date = rc.data_date
-     AND rc.data_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
+     AND to_date(rc.data_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
     JOIN cte_lc_customer cust
       ON cust.letter_of_credit_hashkey = v.letter_of_credit_hashkey
     GROUP BY cust.customer_hashkey
@@ -737,10 +706,10 @@
       ON c.customer_hashkey = s.customer_hashkey
 ),
 cte_prev_bsn_day AS (   
-    SELECT MAX(msr_prd_id) AS prev_bsn_day
+    SELECT MAX(to_date(msr_prd_id, 'yyyyMMdd')) AS prev_bsn_day
     FROM cte_snap_calendar
     WHERE bsn_day_f = 1
-      AND msr_prd_id &lt; to_date(:DATADT, 'yyyyMMdd')
+      AND to_date(msr_prd_id, 'yyyyMMdd') &lt; to_date(:DATADT, 'yyyyMMdd')
 ),
 cte_new_cust AS (  
     SELECT bc.customer_hashkey
@@ -833,10 +802,8 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_acnt_contract_information')
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY acnt_contract_hashkey
-),</t>
-  </si>
-  <si>
-    <t>cte_w4_acnt_contract_type_cur AS (   
+),
+cte_w4_acnt_contract_type_cur AS (   
     SELECT
         acnt_contract_hashkey,
         max_by(con_cat,  source_event_date) AS con_cat,
@@ -845,7 +812,10 @@
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY acnt_contract_hashkey
 ),
-cte_w4_acnt_contract_branch_cur AS (
+</t>
+  </si>
+  <si>
+    <t>cte_w4_acnt_contract_branch_cur AS (
     SELECT
         acnt_contract_hashkey,
         max_by(branch_hashkey, source_event_date) AS branch_hashkey
@@ -1038,8 +1008,8 @@
                        BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180) AND DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -31)
                  THEN 1 ELSE 0 END AS trans_31_120d,
             CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd') &lt; DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180)
-                  AND base.last_trans_date &gt; '19000101'
-                 THEN 1 ELSE 0 END AS trans_121d
+                AND to_date(base.last_trans_date, 'yyyyMMdd') &gt; to_date('19000101', 'yyyyMMdd')
+                THEN 1 ELSE 0 END AS trans_121d
         FROM cte_w4_card_contract base
         LEFT JOIN cte_w4_balance bl ON bl.issuing_hashkey = base.issuing_hashkey
         LEFT JOIN cte_w4_loan_class lcls ON lcls.so_hd = base.issuing_number
@@ -5794,25 +5764,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -5984,14 +5935,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3EEC90-FDD9-42E9-8E8E-DEB77B480DC6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90F5B1A7-2A08-4130-A70D-0C8BBEDB22AD}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDDF1856-D355-4DCF-84E8-16AAC2B17485}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3EEC90-FDD9-42E9-8E8E-DEB77B480DC6}"/>
 </file>